--- a/AfterToken/Configs/GameConfig/Datas/weapon.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/weapon.xlsx
@@ -1264,6 +1264,16 @@
           <t>1,0,0,1</t>
         </is>
       </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>sfx_fire_pistol</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>sfx_reload</t>
+        </is>
+      </c>
       <c r="AR5" t="n">
         <v>2</v>
       </c>
@@ -1400,6 +1410,16 @@
           <t>1,0,0,1</t>
         </is>
       </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>sfx_fire_smg</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>sfx_reload</t>
+        </is>
+      </c>
       <c r="AR6" t="n">
         <v>2</v>
       </c>
@@ -1536,6 +1556,16 @@
           <t>1,0,0,1</t>
         </is>
       </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>sfx_fire_rifle</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>sfx_reload</t>
+        </is>
+      </c>
       <c r="AR7" t="n">
         <v>2</v>
       </c>
@@ -1672,6 +1702,16 @@
           <t>1,0,0,1</t>
         </is>
       </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>sfx_fire_rifle</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>sfx_reload</t>
+        </is>
+      </c>
       <c r="AR8" t="n">
         <v>2</v>
       </c>
@@ -1816,6 +1856,16 @@
       <c r="AM9" t="inlineStr">
         <is>
           <t>SFX_LockOn</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>sfx_fire_rocket</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>sfx_reload</t>
         </is>
       </c>
       <c r="AR9" t="n">
